--- a/backend/template.xlsx
+++ b/backend/template.xlsx
@@ -39,7 +39,7 @@
     <t>Plant :</t>
   </si>
   <si>
-    <t>Mindewadi</t>
+    <t>Mendewadi</t>
   </si>
   <si>
     <t>Test Department :</t>
@@ -140,10 +140,10 @@
 (ΔT &lt;= 1.5 ℃)</t>
   </si>
   <si>
-    <t>CH_DeltaV (mV)</t>
-  </si>
-  <si>
-    <t>DCH_DeltaV (mV)</t>
+    <t>Short CDC CH_DeltaV (mV)</t>
+  </si>
+  <si>
+    <t>Short CDC DCH_DeltaV (mV)</t>
   </si>
   <si>
     <t>Capacity (Ah)</t>
@@ -3521,9 +3521,7 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="23" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="4" t="s">
         <v>0</v>
@@ -4431,9 +4429,7 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="29" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="91" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="B2" s="91"/>
       <c r="C2" s="92"/>
       <c r="D2" s="93" t="s">
         <v>0</v>
